--- a/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_BOM-DALI_LOAD_DigitalLED(V0.2).xlsx
+++ b/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_BOM-DALI_LOAD_DigitalLED(V0.2).xlsx
@@ -1257,7 +1257,7 @@
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>1.2k</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>C22966</t>
+          <t>C22765</t>
         </is>
       </c>
     </row>
